--- a/app/bridge-management/webapp/resources/templates/lookups-template.xlsx
+++ b/app/bridge-management/webapp/resources/templates/lookups-template.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3538,17 +3538,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Updated desc</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -3563,17 +3563,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>REHAB</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Rehabilitation</t>
+          <t>Partial — completed with warnings</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -3588,17 +3588,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>REPLACE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>Error — failed</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
@@ -3613,17 +3613,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>STRENGTHEN</t>
+          <t>RUNNING</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Strengthening</t>
+          <t>Currently running</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
@@ -3638,17 +3638,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Monitor only</t>
+          <t>Pending / not started</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
@@ -3663,17 +3663,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>DECOMMISSION</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Decommission</t>
+          <t>Cancelled by user</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
@@ -3688,17 +3688,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IMMEDIATE</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Immediate (within 24 h)</t>
+          <t>Repair</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -3713,17 +3713,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SHORT_TERM</t>
+          <t>REHAB</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Short term (within 30 days)</t>
+          <t>Rehabilitation</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3738,17 +3738,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MEDIUM_TERM</t>
+          <t>REPLACE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Medium term (within 6 months)</t>
+          <t>Replacement</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -3763,17 +3763,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LONG_TERM</t>
+          <t>STRENGTHEN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Long term (within 2 years)</t>
+          <t>Strengthening</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -3788,17 +3788,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Monitor only</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -3811,25 +3811,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>MEASUREMENT_UNIT</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>tonnes (t)</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>INTERVENTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DECOMMISSION</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Decommission</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>60</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -3838,21 +3838,21 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>IMMEDIATE</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>kilonewtons (kN)</t>
+          <t>Immediate (within 24 h)</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SHORT_TERM</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>metres (m)</t>
+          <t>Short term (within 30 days)</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>MEDIUM_TERM</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>kilometres (km)</t>
+          <t>Medium term (within 6 months)</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -3913,21 +3913,21 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>KPH</t>
+          <t>LONG_TERM</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>kilometres per hour (kph)</t>
+          <t>Long term (within 2 years)</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -3938,21 +3938,21 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>millimetres (mm)</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -3963,17 +3963,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CLASS1</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Class 1 — Special purpose vehicle</t>
+          <t>tonnes (t)</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3988,17 +3988,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CLASS2</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Class 2 — Higher mass / dimensions</t>
+          <t>kilonewtons (kN)</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4013,17 +4013,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CLASS3</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Class 3 — Restricted access vehicle</t>
+          <t>metres (m)</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -4038,17 +4038,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CLASS4</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Class 4 — Unique configuration</t>
+          <t>kilometres (km)</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -4063,17 +4063,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HML</t>
+          <t>KPH</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HML — Higher Mass Limits</t>
+          <t>kilometres per hour (kph)</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -4088,17 +4088,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B_DOUBLE</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B-Double</t>
+          <t>millimetres (mm)</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4111,50 +4111,50 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>B_TRIPLE</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>B-Triple</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>70</v>
-      </c>
-      <c r="E146" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>CLASS1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Class 1 — Special purpose vehicle</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Not assessed</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>80</v>
-      </c>
-      <c r="E147" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>CLASS2</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Class 2 — Higher mass / dimensions</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -4163,21 +4163,21 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_DECISION</t>
+          <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>CLASS3</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Class 3 — Restricted access vehicle</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -4188,21 +4188,21 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_DECISION</t>
+          <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>APPROVED_WITH_CONDITIONS</t>
+          <t>CLASS4</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Approved with conditions</t>
+          <t>Class 4 — Unique configuration</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -4213,21 +4213,21 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_DECISION</t>
+          <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>DENIED</t>
+          <t>HML</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Denied</t>
+          <t>HML — Higher Mass Limits</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -4238,21 +4238,21 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_DECISION</t>
+          <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>B_DOUBLE</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Pending — saved for review</t>
+          <t>B-Double</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -4261,50 +4261,50 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>PERMIT_STATUS</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>DRAFT</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Draft — not yet submitted</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10</v>
-      </c>
-      <c r="E152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>NHVR_APPROVAL_CLASS</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>B_TRIPLE</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>B-Triple</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>PERMIT_STATUS</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SUBMITTED</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Submitted for review</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>20</v>
-      </c>
-      <c r="E153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>NHVR_APPROVAL_CLASS</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Not assessed</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -4313,21 +4313,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PERMIT_STATUS</t>
+          <t>PERMIT_DECISION</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Under NHVR review</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -4338,21 +4338,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PERMIT_STATUS</t>
+          <t>PERMIT_DECISION</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>APPROVED_WITH_CONDITIONS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with conditions</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PERMIT_STATUS</t>
+          <t>PERMIT_DECISION</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>DENIED</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Denied</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PERMIT_STATUS</t>
+          <t>PERMIT_DECISION</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Pending — saved for review</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4413,17 +4413,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>SINGLE_TRIP</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Single-trip permit</t>
+          <t>Draft — not yet submitted</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
@@ -4438,17 +4438,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>PERIODIC</t>
+          <t>SUBMITTED</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Periodic / annual permit</t>
+          <t>Submitted for review</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -4463,17 +4463,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>OVERSIZE</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Oversize load</t>
+          <t>Under NHVR review</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
@@ -4488,17 +4488,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>OVERMASS</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Overmass load</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -4513,17 +4513,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>CLASS_1</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Class 1 special purpose</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
@@ -4536,25 +4536,25 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>POSTING_STATUS</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>UNRESTRICTED</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Open to all lawful loads</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10</v>
-      </c>
-      <c r="E163" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>PERMIT_STATUS</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Expired</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -4563,21 +4563,21 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>POSTING_STATUS</t>
+          <t>PERMIT_TYPE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>POSTED</t>
+          <t>SINGLE_TRIP</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Load limits in effect</t>
+          <t>Single-trip permit</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>POSTING_STATUS</t>
+          <t>PERMIT_TYPE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>PERIODIC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Reduced capacity</t>
+          <t>Periodic / annual permit</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -4613,73 +4613,73 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>POSTING_STATUS</t>
+          <t>PERMIT_TYPE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OVERSIZE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bridge closed</t>
+          <t>Oversize load</t>
         </is>
       </c>
       <c r="D166" t="n">
+        <v>30</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PERMIT_TYPE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OVERMASS</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Overmass load</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
         <v>40</v>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>PROGRAMME_STATUS</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>DRAFT</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Draft programme</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>PROGRAMME_STATUS</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PERMIT_TYPE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CLASS_1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Class 1 special purpose</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>50</v>
+      </c>
+      <c r="E168" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -4688,21 +4688,21 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PROGRAMME_STATUS</t>
+          <t>POSTING_STATUS</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>FUNDED</t>
+          <t>UNRESTRICTED</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Funded</t>
+          <t>Open to all lawful loads</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -4713,21 +4713,21 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PROGRAMME_STATUS</t>
+          <t>POSTING_STATUS</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>IN_DELIVERY</t>
+          <t>POSTED</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>In delivery</t>
+          <t>Load limits in effect</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -4738,21 +4738,21 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PROGRAMME_STATUS</t>
+          <t>POSTING_STATUS</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>REDUCED</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Reduced capacity</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PROGRAMME_STATUS</t>
+          <t>POSTING_STATUS</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Bridge closed</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
@@ -4788,17 +4788,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>AS_5100</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AS 5100 — Australian standard</t>
+          <t>Draft programme</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -4813,17 +4813,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>AASHTO_LRFR</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AASHTO LRFR</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -4838,17 +4838,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>WORKING_STRESS</t>
+          <t>FUNDED</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Working-stress method</t>
+          <t>Funded</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -4863,17 +4863,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LOAD_FACTOR</t>
+          <t>IN_DELIVERY</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Load-factor method</t>
+          <t>In delivery</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -4888,17 +4888,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FE_ANALYSIS</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Finite-element analysis</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -4911,25 +4911,25 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_DIRECTION</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Both directions</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PROGRAMME_STATUS</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>60</v>
+      </c>
+      <c r="E178" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -4938,21 +4938,21 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>INCREASING</t>
+          <t>AS_5100</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Increasing chainage</t>
+          <t>AS 5100 — Australian standard</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>DECREASING</t>
+          <t>AASHTO_LRFR</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Decreasing chainage</t>
+          <t>AASHTO LRFR</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
@@ -4988,21 +4988,21 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>NORTHBOUND</t>
+          <t>WORKING_STRESS</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Northbound</t>
+          <t>Working-stress method</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
@@ -5013,21 +5013,21 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBOUND</t>
+          <t>LOAD_FACTOR</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Southbound</t>
+          <t>Load-factor method</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -5038,21 +5038,21 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>EASTBOUND</t>
+          <t>FE_ANALYSIS</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Eastbound</t>
+          <t>Finite-element analysis</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
@@ -5061,25 +5061,25 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_DIRECTION</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>WESTBOUND</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Westbound</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ACT:CANBERRA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -5088,17 +5088,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>NSW:SYDNEY_METRO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Active and enforceable</t>
+          <t>Sydney Metro</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -5113,21 +5113,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NT:DARWIN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Awaiting approval</t>
+          <t>Darwin</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SUPERSEDED</t>
+          <t>QLD:BRISBANE_METRO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Replaced by newer restriction</t>
+          <t>Brisbane Metro</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LIFTED</t>
+          <t>SA:ADELAIDE_METRO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No longer in effect</t>
+          <t>Adelaide Metro</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5188,21 +5188,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>TAS:HOBART</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Past validity date</t>
+          <t>Hobart</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5211,200 +5211,200 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>MASS_LIMIT</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>Mass limit (tonnes)</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="n">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>VIC:MELBOURNE_METRO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Melbourne Metro</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
         <v>10</v>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>AXLE_LIMIT</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>Axle group limit</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="n">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>WA:PERTH_METRO</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Perth Metro</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NSW:HUNTER</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Hunter</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
         <v>20</v>
       </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>HEIGHT_LIMIT</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>Clearance height limit</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>WIDTH_LIMIT</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle width limit</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>NT:KATHERINE</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>20</v>
+      </c>
+      <c r="E193" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>LENGTH_LIMIT</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle length limit</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>QLD:GOLD_COAST</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>20</v>
+      </c>
+      <c r="E194" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>SPEED_LIMIT</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>Reduced speed on structure</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SA:BAROSSA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Barossa</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>20</v>
+      </c>
+      <c r="E195" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>LANE_CLOSURE</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>Lane closure</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>TAS:LAUNCESTON</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Launceston</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>20</v>
+      </c>
+      <c r="E196" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>RESTRICTION_TYPE</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>FULL_CLOSURE</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>Full closure</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>VIC:BARWON</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Barwon</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>20</v>
+      </c>
+      <c r="E197" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -5413,21 +5413,21 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>WA:KIMBERLEY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Low risk band</t>
+          <t>Kimberley</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>NSW:ILLAWARRA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Medium risk band</t>
+          <t>Illawarra</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -5463,17 +5463,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NT:ALICE_SPRINGS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>High risk band</t>
+          <t>Alice Springs</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -5488,21 +5488,21 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VERY_HIGH</t>
+          <t>QLD:SUNSHINE_COAST</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Very high risk band</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>SA:EYRE_PENINSULA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Critical risk band</t>
+          <t>Eyre Peninsula</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -5536,125 +5536,125 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>ROUTE_CLASS</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>General Freight</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TAS:NORTH_WEST</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>North West</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>30</v>
+      </c>
+      <c r="E203" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>ROUTE_CLASS</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>B_DOUBLE</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>B-Double</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>VIC:GRAMPIANS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Grampians</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>30</v>
+      </c>
+      <c r="E204" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>ROUTE_CLASS</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>ROAD_TRAIN</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>Road Train</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="n">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>WA:PILBARA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Pilbara</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
         <v>30</v>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>ROUTE_CLASS</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>HML</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>HML — Higher Mass Limits</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="n">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>NSW:CENTRAL_COAST</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Central Coast</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
         <v>40</v>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>ROUTE_CLASS</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>PBS</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>PBS — Performance Based Standards</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>NT:BARKLY</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Barkly</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>40</v>
+      </c>
+      <c r="E207" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -5663,21 +5663,21 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ROUTE_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>QLD:DARLING_DOWNS</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Active and operating</t>
+          <t>Darling Downs</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ROUTE_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SA:FLINDERS_RANGES</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Temporarily suspended</t>
+          <t>Flinders Ranges</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ROUTE_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>TAS:WEST_COAST</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Under review / re-assessment</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -5738,17 +5738,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ROUTE_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>RETIRED</t>
+          <t>VIC:LODDON_MALLEE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Retired / decommissioned</t>
+          <t>Loddon Mallee</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -5761,125 +5761,125 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>SCOUR_RISK</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Low scour risk</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>WA:GASCOYNE</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Gascoyne</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>40</v>
+      </c>
+      <c r="E212" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>SCOUR_RISK</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>Medium scour risk</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NSW:NORTH_COAST</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>50</v>
+      </c>
+      <c r="E213" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>SCOUR_RISK</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>High scour risk</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>NT:EAST_ARNHEM</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>East Arnhem</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>50</v>
+      </c>
+      <c r="E214" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>SCOUR_RISK</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>Critical scour risk</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>QLD:CENTRAL_QLD</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Central Queensland</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>50</v>
+      </c>
+      <c r="E215" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>SCOUR_RISK</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>Not yet assessed</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="n">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SA:LIMESTONE_COAST</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Limestone Coast</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
         <v>50</v>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -5888,21 +5888,21 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NSW</t>
+          <t>TAS:EAST_COAST</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -5913,21 +5913,21 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VIC:HUME</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Hume</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5938,21 +5938,21 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>WA:MIDWEST</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Queensland</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>NSW:MID_NORTH_COAST</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Western Australia</t>
+          <t>Mid North Coast</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5988,21 +5988,21 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>QLD:FAR_NORTH_QLD</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>South Australia</t>
+          <t>Far North Queensland</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6013,17 +6013,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TAS</t>
+          <t>SA:MURRAYLANDS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tasmania</t>
+          <t>Murraylands</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -6038,21 +6038,21 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VIC:GIPPSLAND</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Northern Territory</t>
+          <t>Gippsland</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6063,21 +6063,21 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>WA:WHEATBELT</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Australian Capital Territory</t>
+          <t>Wheatbelt</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -6086,100 +6086,100 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURAL_ADEQUACY</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>ADEQUATE</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>Adequate for design loads</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>NSW:NEW_ENGLAND</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>New England</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>70</v>
+      </c>
+      <c r="E225" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURAL_ADEQUACY</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>MARGINAL</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>Marginal — monitor</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>QLD:NORTH_QLD</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>North Queensland</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>70</v>
+      </c>
+      <c r="E226" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURAL_ADEQUACY</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>DEFICIENT</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>Structurally deficient</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SA:RIVERLAND</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Riverland</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>70</v>
+      </c>
+      <c r="E227" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURAL_ADEQUACY</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>WA:GOLDFIELDS_ESPERANCE</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Goldfields-Esperance</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>70</v>
+      </c>
+      <c r="E228" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -6188,21 +6188,21 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NSW:RIVERINA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Riverina</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -6213,21 +6213,21 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>QLD:WIDE_BAY</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Wide Bay</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -6238,21 +6238,21 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>SA:YORKE_PENINSULA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yorke Peninsula</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -6263,21 +6263,21 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VERY_HIGH</t>
+          <t>WA:GREAT_SOUTHERN</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Great Southern</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>NSW:CENTRAL_WEST</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Central West</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -6311,100 +6311,100 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURE_TYPE</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>ARCH</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>Arch bridge</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>WA:SOUTH_WEST</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>90</v>
+      </c>
+      <c r="E234" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURE_TYPE</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>BEAM</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>Beam / girder bridge</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>NSW:FAR_WEST</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Far West</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>100</v>
+      </c>
+      <c r="E235" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURE_TYPE</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>SUSPENSION</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>Suspension bridge</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>WA:PEEL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Peel</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>100</v>
+      </c>
+      <c r="E236" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURE_TYPE</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>CABLE_STAYED</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>Cable-stayed bridge</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>REGION</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>NSW:SOUTH_COAST</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>South Coast</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>110</v>
+      </c>
+      <c r="E237" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -6413,21 +6413,21 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>STRUCTURE_TYPE</t>
+          <t>RESTRICTION_DIRECTION</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>TRUSS</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Truss bridge</t>
+          <t>Both directions</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>STRUCTURE_TYPE</t>
+          <t>RESTRICTION_DIRECTION</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>INCREASING</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Slab bridge</t>
+          <t>Increasing chainage</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>STRUCTURE_TYPE</t>
+          <t>RESTRICTION_DIRECTION</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>BOX_GIRDER</t>
+          <t>DECREASING</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Box-girder bridge</t>
+          <t>Decreasing chainage</t>
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>STRUCTURE_TYPE</t>
+          <t>RESTRICTION_DIRECTION</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>CULVERT</t>
+          <t>NORTHBOUND</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Culvert</t>
+          <t>Northbound</t>
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -6511,75 +6511,75 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>VEHICLE_CLASS</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>A_DOUBLE</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>A-Double</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>10</v>
-      </c>
-      <c r="E242" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_DIRECTION</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHBOUND</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Southbound</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>VEHICLE_CLASS</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>B_DOUBLE</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>B-Double</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>20</v>
-      </c>
-      <c r="E243" t="inlineStr">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_DIRECTION</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>EASTBOUND</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Eastbound</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>VEHICLE_CLASS</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>B_TRAIN</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>B-Train</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>30</v>
-      </c>
-      <c r="E244" t="inlineStr">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_DIRECTION</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>WESTBOUND</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Westbound</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -6588,21 +6588,21 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>VEHICLE_CLASS</t>
+          <t>RESTRICTION_STATUS</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ROAD_TRAIN</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Road Train</t>
+          <t>Active and enforceable</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6613,21 +6613,21 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>VEHICLE_CLASS</t>
+          <t>RESTRICTION_STATUS</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PBS_1</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>PBS Level 1</t>
+          <t>Awaiting approval</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>VEHICLE_CLASS</t>
+          <t>RESTRICTION_STATUS</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PBS_2</t>
+          <t>SUPERSEDED</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PBS Level 2</t>
+          <t>Replaced by newer restriction</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VEHICLE_CLASS</t>
+          <t>RESTRICTION_STATUS</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PBS_3</t>
+          <t>LIFTED</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>PBS Level 3</t>
+          <t>No longer in effect</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -6688,48 +6688,1573 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
+          <t>RESTRICTION_STATUS</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Past validity date</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>50</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>MASS_LIMIT</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Mass limit (tonnes)</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>AXLE_LIMIT</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Axle group limit</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>HEIGHT_LIMIT</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Clearance height limit</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>WIDTH_LIMIT</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle width limit</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>LENGTH_LIMIT</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle length limit</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>SPEED_LIMIT</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Reduced speed on structure</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>LANE_CLOSURE</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Lane closure</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>RESTRICTION_TYPE</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>FULL_CLOSURE</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Full closure</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>RISK_BAND</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Low risk band</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>10</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>RISK_BAND</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Medium risk band</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>20</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>RISK_BAND</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>High risk band</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>30</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>RISK_BAND</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>VERY_HIGH</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Very high risk band</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>40</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>RISK_BAND</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Critical risk band</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>50</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>ROUTE_CLASS</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>General Freight</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ROUTE_CLASS</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>B_DOUBLE</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>B-Double</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>ROUTE_CLASS</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>ROAD_TRAIN</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Road Train</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>ROUTE_CLASS</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>HML</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>HML — Higher Mass Limits</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>ROUTE_CLASS</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>PBS</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>PBS — Performance Based Standards</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ROUTE_STATUS</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Active and operating</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>10</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ROUTE_STATUS</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Temporarily suspended</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>20</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ROUTE_STATUS</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>UNDER_REVIEW</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Under review / re-assessment</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>30</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ROUTE_STATUS</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>RETIRED</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Retired / decommissioned</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>40</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>SCOUR_RISK</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Low scour risk</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>SCOUR_RISK</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Medium scour risk</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>SCOUR_RISK</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>High scour risk</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>SCOUR_RISK</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Critical scour risk</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>SCOUR_RISK</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Not yet assessed</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>New South Wales</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>10</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>20</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Queensland</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>30</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Western Australia</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>40</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>South Australia</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>50</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Tasmania</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>60</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Northern Territory</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>70</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>80</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_ADEQUACY</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>ADEQUATE</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Adequate for design loads</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_ADEQUACY</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>MARGINAL</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Marginal — monitor</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_ADEQUACY</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>DEFICIENT</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Structurally deficient</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_ADEQUACY</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>10</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>20</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>30</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>VERY_HIGH</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>40</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>50</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>ARCH</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Arch bridge</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>BEAM</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Beam / girder bridge</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>SUSPENSION</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Suspension bridge</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>CABLE_STAYED</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Cable-stayed bridge</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>TRUSS</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Truss bridge</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Slab bridge</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>BOX_GIRDER</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Box-girder bridge</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>CULVERT</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Culvert</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>UAT_06_TEST</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>UAT_OK</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mass upload UAT</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>99</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
           <t>VEHICLE_CLASS</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>A_DOUBLE</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>A-Double</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>B_DOUBLE</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>B-Double</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>B_TRAIN</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>B-Train</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>ROAD_TRAIN</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Road Train</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>PBS_1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>PBS Level 1</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>PBS_2</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>PBS Level 2</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>PBS_3</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>PBS Level 3</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>VEHICLE_CLASS</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>GENERAL</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
         <is>
           <t>General access</t>
         </is>
       </c>
-      <c r="D249" t="n">
+      <c r="D310" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
         <is>
           <t>VEHICLE_CLASS</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>OVERSIZE</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C311" s="2" t="inlineStr">
         <is>
           <t>Oversize / overdimension</t>
         </is>
       </c>
-      <c r="D250" t="n">
+      <c r="D311" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E311" s="2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -6747,7 +8272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7015,202 +8540,194 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INTERVENTION_TYPE</t>
+          <t>INTEGRATION_STATUS</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Repair, rehab, replace etc.</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAINTENANCE_URGENCY</t>
+          <t>INTERVENTION_TYPE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maintenance urgency band</t>
+          <t>Repair, rehab, replace etc.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MEASUREMENT_UNIT</t>
+          <t>MAINTENANCE_URGENCY</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>t, m, kph, kN etc. (Restrictions, BridgeDetail)</t>
+          <t>Maintenance urgency band</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NHVR_APPROVAL_CLASS</t>
+          <t>MEASUREMENT_UNIT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NHVR PBS approval class (BridgeForm)</t>
+          <t>t, m, kph, kN etc. (Restrictions, BridgeDetail)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PERMIT_DECISION</t>
+          <t>NHVR_APPROVAL_CLASS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Approve / Deny / Conditions (Permits)</t>
+          <t>NHVR PBS approval class (BridgeForm)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PERMIT_STATUS</t>
+          <t>PERMIT_DECISION</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Permit status filter (Permits)</t>
+          <t>Approve / Deny / Conditions (Permits)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PERMIT_TYPE</t>
+          <t>PERMIT_STATUS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Permit type filter (Permits)</t>
+          <t>Permit status filter (Permits)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POSTING_STATUS</t>
+          <t>PERMIT_TYPE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridge posting status (BridgeForm) — server-validated enum</t>
+          <t>Permit type filter (Permits)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PROGRAMME_STATUS</t>
+          <t>POSTING_STATUS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Investment programme status</t>
+          <t>Bridge posting status (BridgeForm) — server-validated enum</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RATING_METHOD</t>
+          <t>PROGRAMME_STATUS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bridge rating method</t>
+          <t>Investment programme status</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RESTRICTION_DIRECTION</t>
+          <t>RATING_METHOD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Both / Increasing / Decreasing / NESW (Restrictions)</t>
+          <t>Bridge rating method</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RESTRICTION_STATUS</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Restriction status (Restrictions)</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RESTRICTION_TYPE</t>
+          <t>RESTRICTION_DIRECTION</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Restriction type (Restrictions)</t>
+          <t>Both / Increasing / Decreasing / NESW (Restrictions)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RISK_BAND</t>
+          <t>RESTRICTION_STATUS</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7218,44 +8735,44 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Risk band Low/Medium/High/Critical (Bridges filter)</t>
+          <t>Restriction status (Restrictions)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ROUTE_CLASS</t>
+          <t>RESTRICTION_TYPE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PBS, HML, B-Double etc. (FreightRoutes)</t>
+          <t>Restriction type (Restrictions)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ROUTE_STATUS</t>
+          <t>RISK_BAND</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Active / Suspended / Under Review (FreightRoutes)</t>
+          <t>Risk band Low/Medium/High/Critical (Bridges filter)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCOUR_RISK</t>
+          <t>ROUTE_CLASS</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7263,80 +8780,121 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scour risk (BridgeForm) — server-validated enum</t>
+          <t>PBS, HML, B-Double etc. (FreightRoutes)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>ROUTE_STATUS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Australian state codes</t>
+          <t>Active / Suspended / Under Review (FreightRoutes)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STRUCTURAL_ADEQUACY</t>
+          <t>SCOUR_RISK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Adequate / Marginal / Deficient (BridgeDetail)</t>
+          <t>Scour risk (BridgeForm) — server-validated enum</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STRUCTURAL_RISK</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Structural risk band</t>
+          <t>Australian state codes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STRUCTURE_TYPE</t>
+          <t>STRUCTURAL_ADEQUACY</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Beam, Arch, Truss etc. (BridgeForm)</t>
+          <t>Adequate / Marginal / Deficient (BridgeDetail)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>STRUCTURAL_RISK</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Structural risk band</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STRUCTURE_TYPE</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Beam, Arch, Truss etc. (BridgeForm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UAT_06_TEST</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>VEHICLE_CLASS</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B42" t="n">
         <v>9</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>B-Double, Road Train, PBS levels (BridgeDetail)</t>
         </is>
